--- a/02table/TableS4_Gene_Ontology_for_modules.xlsx
+++ b/02table/TableS4_Gene_Ontology_for_modules.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11113"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D1DB3C6-862E-2E43-9E14-18F51906D14F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B68964C2-30E0-994C-9AC4-7EC5111FC7F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-34180" yWindow="7520" windowWidth="34180" windowHeight="12640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="34620" yWindow="2080" windowWidth="30240" windowHeight="16620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -8272,20 +8272,6 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>BP, Biological process; MF, molecular function; CC, cellular component</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>a</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
       <t>Gene ratio for a given GO term in the analyzed gene list.</t>
     </r>
   </si>
@@ -8305,6 +8291,20 @@
   </si>
   <si>
     <t>Table S4 Gene Ontology enrichment analysis was performed using the genes in each module of the co-expression network constructed from the hybrid population.</t>
+  </si>
+  <si>
+    <r>
+      <t>c</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>BP, Biological process; MF, molecular function; CC, cellular component</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -8723,7 +8723,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>2732</v>
+        <v>2731</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.25">
@@ -39990,17 +39990,17 @@
     </row>
     <row r="1081" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A1081" s="14" t="s">
-        <v>2730</v>
+        <v>2729</v>
       </c>
     </row>
     <row r="1082" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A1082" s="14" t="s">
-        <v>2731</v>
+        <v>2730</v>
       </c>
     </row>
     <row r="1083" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A1083" s="14" t="s">
-        <v>2729</v>
+        <v>2732</v>
       </c>
     </row>
     <row r="1470" spans="6:6" x14ac:dyDescent="0.2">
